--- a/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
+++ b/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t xml:space="preserve">Código</t>
   </si>
@@ -32,6 +32,9 @@
     <t xml:space="preserve">Nombre</t>
   </si>
   <si>
+    <t xml:space="preserve">Departamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Costo</t>
   </si>
   <si>
@@ -45,6 +48,12 @@
   </si>
   <si>
     <t xml:space="preserve">Precio Mayoreo en descuento de clientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obligatorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcional</t>
   </si>
   <si>
     <t xml:space="preserve">21</t>
@@ -73,7 +82,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -98,6 +107,30 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -147,7 +180,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -156,11 +189,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -181,14 +226,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="8.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="38.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -201,7 +248,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -210,46 +257,48 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="I2" s="3"/>
+    </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H4" s="2"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H5" s="2"/>
+      <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H8" s="2"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H10" s="2"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -267,17 +316,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.3671875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="38.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="38.46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -290,7 +340,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -299,37 +349,69 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="0" t="n">
+      <c r="F3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
+++ b/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
   <si>
     <t xml:space="preserve">Código</t>
   </si>
@@ -29,12 +29,12 @@
     <t xml:space="preserve">Marca</t>
   </si>
   <si>
+    <t xml:space="preserve">Departamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nombre</t>
   </si>
   <si>
-    <t xml:space="preserve">Departamento</t>
-  </si>
-  <si>
     <t xml:space="preserve">Costo</t>
   </si>
   <si>
@@ -56,13 +56,16 @@
     <t xml:space="preserve">Opcional</t>
   </si>
   <si>
-    <t xml:space="preserve">21</t>
+    <t xml:space="preserve">1</t>
   </si>
   <si>
     <t xml:space="preserve">Aguas Inc</t>
   </si>
   <si>
-    <t xml:space="preserve">Agua embotellada (2.5 L)</t>
+    <t xml:space="preserve">Aguas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua embotellada (1L)</t>
   </si>
   <si>
     <t xml:space="preserve">15.00</t>
@@ -72,6 +75,12 @@
   </si>
   <si>
     <t xml:space="preserve">Si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua embotellada (2L)</t>
   </si>
 </sst>
 </file>
@@ -82,7 +91,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -120,13 +129,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -180,7 +182,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,10 +204,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -227,9 +225,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.45"/>
@@ -245,10 +244,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -316,13 +315,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="8.37890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.16"/>
@@ -337,10 +336,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -366,11 +365,11 @@
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -378,13 +377,13 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -398,21 +397,42 @@
       <c r="C3" s="0" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="0" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="0" t="n">
         <v>8</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
+++ b/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
   <si>
     <t xml:space="preserve">Código</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve">Precio Mayoreo en descuento de clientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad</t>
   </si>
   <si>
     <t xml:space="preserve">Obligatorio</t>
@@ -199,11 +202,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -224,8 +227,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.94"/>
@@ -265,9 +268,13 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I4" s="3"/>
@@ -276,10 +283,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I6" s="4"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I7" s="4"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="3"/>
@@ -294,10 +301,10 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I12" s="4"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I13" s="4"/>
+      <c r="I13" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -315,7 +322,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="8.37890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.22"/>
@@ -357,80 +364,89 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>10</v>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>8</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>8</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3"/>
     </row>

--- a/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
+++ b/static/templates/SmartVenta_plantilla_importacion_productos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Reporte" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t xml:space="preserve">Código</t>
   </si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">Precio Mayoreo en descuento de clientes</t>
   </si>
   <si>
+    <t xml:space="preserve">Unidad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cantidad</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
     <t xml:space="preserve">Opcional</t>
   </si>
   <si>
+    <t xml:space="preserve">PZ|KG|CO</t>
+  </si>
+  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -78,6 +84,9 @@
   </si>
   <si>
     <t xml:space="preserve">Si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -185,7 +194,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -204,6 +213,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -227,8 +240,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.94"/>
@@ -271,6 +284,9 @@
       <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I2" s="3"/>
@@ -278,15 +294,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I4" s="3"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I6" s="5"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I7" s="5"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="3"/>
@@ -301,10 +318,10 @@
       <c r="I11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I12" s="5"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I13" s="5"/>
+      <c r="I13" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -322,7 +339,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.37890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.22"/>
@@ -334,6 +351,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="38.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -367,86 +385,95 @@
       <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>8</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="0" t="n">
         <v>5</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>8</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I4" s="3"/>
     </row>
